--- a/en/downloads/data-excel/6.1.1.1.xlsx
+++ b/en/downloads/data-excel/6.1.1.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2A4B65-3965-4F2D-99C2-E5ED48ABA6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9015" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,15 +26,6 @@
     <t>(в процентах)</t>
   </si>
   <si>
-    <t xml:space="preserve"> 6.1.1.2b Доля проб воды, не отвечающих гигиеническим нормативам</t>
-  </si>
-  <si>
-    <t>6.1.1.2b Суунун гигиеналык нормативдерге жооп бербеген сынамыктарынын үлүшү</t>
-  </si>
-  <si>
-    <t>6.1.1.2b Percentage of water samples that do not comply with hygiene standards</t>
-  </si>
-  <si>
     <t>(пайыз менен)</t>
   </si>
   <si>
@@ -59,12 +51,21 @@
   </si>
   <si>
     <t>Samples tested according to microbiological indicators</t>
+  </si>
+  <si>
+    <t>6.1.1.1 Суунун гигиеналык нормативдерге жооп бербеген сынамыктарынын үлүшү</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.1.1.1 Доля проб воды, не отвечающих гигиеническим нормативам</t>
+  </si>
+  <si>
+    <t>6.1.1.1 Percentage of water samples that do not comply with hygiene standards</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -158,24 +159,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -195,9 +193,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -229,9 +224,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -269,9 +264,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -306,7 +301,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -341,7 +336,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -514,135 +509,139 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="36.140625" style="8" customWidth="1"/>
-    <col min="4" max="20" width="8.5703125" style="8" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="3" width="36.140625" style="7" customWidth="1"/>
+    <col min="4" max="20" width="8.5703125" style="7" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+    </row>
+    <row r="2" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="3" spans="1:21" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+    </row>
+    <row r="4" spans="1:21" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="B4" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="10">
+        <v>2007</v>
+      </c>
+      <c r="E4" s="10">
+        <v>2008</v>
+      </c>
+      <c r="F4" s="10">
+        <v>2009</v>
+      </c>
+      <c r="G4" s="10">
+        <v>2010</v>
+      </c>
+      <c r="H4" s="10">
+        <v>2011</v>
+      </c>
+      <c r="I4" s="10">
+        <v>2012</v>
+      </c>
+      <c r="J4" s="10">
+        <v>2013</v>
+      </c>
+      <c r="K4" s="10">
+        <v>2014</v>
+      </c>
+      <c r="L4" s="10">
+        <v>2015</v>
+      </c>
+      <c r="M4" s="10">
+        <v>2016</v>
+      </c>
+      <c r="N4" s="10">
+        <v>2017</v>
+      </c>
+      <c r="O4" s="10">
+        <v>2018</v>
+      </c>
+      <c r="P4" s="10">
+        <v>2019</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>2020</v>
+      </c>
+      <c r="R4" s="10">
+        <v>2021</v>
+      </c>
+      <c r="S4" s="10">
+        <v>2022</v>
+      </c>
+      <c r="T4" s="10">
+        <v>2023</v>
+      </c>
+      <c r="U4" s="10">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-    </row>
-    <row r="4" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+    <row r="5" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="B5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>10</v>
-      </c>
-      <c r="D4" s="11">
-        <v>2007</v>
-      </c>
-      <c r="E4" s="11">
-        <v>2008</v>
-      </c>
-      <c r="F4" s="11">
-        <v>2009</v>
-      </c>
-      <c r="G4" s="11">
-        <v>2010</v>
-      </c>
-      <c r="H4" s="11">
-        <v>2011</v>
-      </c>
-      <c r="I4" s="11">
-        <v>2012</v>
-      </c>
-      <c r="J4" s="11">
-        <v>2013</v>
-      </c>
-      <c r="K4" s="11">
-        <v>2014</v>
-      </c>
-      <c r="L4" s="11">
-        <v>2015</v>
-      </c>
-      <c r="M4" s="11">
-        <v>2016</v>
-      </c>
-      <c r="N4" s="11">
-        <v>2017</v>
-      </c>
-      <c r="O4" s="11">
-        <v>2018</v>
-      </c>
-      <c r="P4" s="11">
-        <v>2019</v>
-      </c>
-      <c r="Q4" s="16">
-        <v>2020</v>
-      </c>
-      <c r="R4" s="11">
-        <v>2021</v>
-      </c>
-      <c r="S4" s="11">
-        <v>2022</v>
-      </c>
-      <c r="T4" s="11">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>13</v>
       </c>
       <c r="D5" s="1">
         <v>2.1</v>
@@ -680,31 +679,34 @@
       <c r="O5" s="2">
         <v>1.7</v>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="7">
         <v>1.4</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="R5" s="13">
+      <c r="R5" s="7">
         <v>0.9</v>
       </c>
-      <c r="S5" s="13">
+      <c r="S5" s="7">
         <v>1.8</v>
       </c>
-      <c r="T5" s="13">
+      <c r="T5" s="7">
         <v>1.4</v>
       </c>
+      <c r="U5" s="7">
+        <v>1.3</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="14" t="s">
+    <row r="6" spans="1:21" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>14</v>
+      <c r="C6" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="D6" s="3">
         <v>10.6</v>
@@ -730,32 +732,35 @@
       <c r="K6" s="3">
         <v>6.5</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="3">
         <v>7.7</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="3">
         <v>8.4</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6" s="3">
         <v>8.1</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="3">
         <v>8.1999999999999993</v>
       </c>
-      <c r="P6" s="4">
+      <c r="P6" s="3">
         <v>8.6</v>
       </c>
-      <c r="Q6" s="17">
+      <c r="Q6" s="15">
         <v>7</v>
       </c>
-      <c r="R6" s="4">
+      <c r="R6" s="3">
         <v>6.5</v>
       </c>
-      <c r="S6" s="4">
+      <c r="S6" s="3">
         <v>8.4</v>
       </c>
-      <c r="T6" s="4">
+      <c r="T6" s="3">
         <v>8.1999999999999993</v>
+      </c>
+      <c r="U6" s="3">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
